--- a/ProjectFiles/CS4013ProjectTeamContributionsGroup9.xlsx
+++ b/ProjectFiles/CS4013ProjectTeamContributionsGroup9.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24436739\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24436739\Development\Timetable-System-Project\ProjectFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0305E0D4-599F-42F4-978E-3193FCBE2219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C138407C-5C97-4415-91B8-6A3D8320234A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t xml:space="preserve">This contributions document must be agreed by all team members </t>
   </si>
@@ -59,9 +59,6 @@
     <t>Testing</t>
   </si>
   <si>
-    <t>name 1</t>
-  </si>
-  <si>
     <t>name 2</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>File Name</t>
   </si>
   <si>
-    <t>name1</t>
-  </si>
-  <si>
     <t>name2</t>
   </si>
   <si>
@@ -89,12 +83,6 @@
     <t>name4</t>
   </si>
   <si>
-    <t>filename1</t>
-  </si>
-  <si>
-    <t>filename2</t>
-  </si>
-  <si>
     <t>filename3</t>
   </si>
   <si>
@@ -147,6 +135,18 @@
   </si>
   <si>
     <t>Everyone</t>
+  </si>
+  <si>
+    <t>Cian O'Shaughnessy</t>
+  </si>
+  <si>
+    <t>Module.Java</t>
+  </si>
+  <si>
+    <t>User.Java</t>
+  </si>
+  <si>
+    <t>Implemented the get and set classes of LabGroup and Module Name</t>
   </si>
 </sst>
 </file>
@@ -229,13 +229,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -563,24 +563,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -604,10 +604,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>1</v>
+        <v>24436739</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
         <v>0.25</v>
@@ -627,7 +627,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3">
         <v>0.2</v>
@@ -647,7 +647,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3">
         <v>0.15</v>
@@ -667,7 +667,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3">
         <v>0.4</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>3</v>
@@ -719,24 +719,27 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
       </c>
       <c r="F12" s="3">
         <f>SUM(B12:E12)</f>
@@ -745,7 +748,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" ref="F13:F21" si="1">SUM(B13:E13)</f>
@@ -754,7 +757,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" si="1"/>
@@ -763,7 +766,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="1"/>
@@ -772,7 +775,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
@@ -781,7 +784,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
@@ -790,7 +793,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" si="1"/>
@@ -799,7 +802,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
@@ -808,7 +811,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
@@ -817,7 +820,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="1"/>
@@ -829,10 +832,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F23" s="3"/>
     </row>
@@ -842,7 +845,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -851,31 +854,31 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="6">
+        <v>45966</v>
+      </c>
+      <c r="B27" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="C27" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="8">
-        <v>45966</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
-      </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F27" s="3"/>
     </row>
